--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:42:58 UTC</t>
+          <t>2026-06-11 05:02:28 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:02:28 UTC</t>
+          <t>2026-06-11 07:43:48 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 07:43:48 UTC</t>
+          <t>2026-06-14 21:52:55 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:52:55 UTC</t>
+          <t>2026-06-15 07:08:04 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>raw_dataset_selection</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>filtercake_sugar_average_to_date</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>average_to_date</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>removed_from_X</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Column name contains an automatic target-leakage marker.</t>
         </is>
       </c>
     </row>
@@ -468,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +522,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>raw_dataset_selection</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kept_as_final_target</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Selected final targets are not removed from y.</t>
         </is>
       </c>
     </row>
@@ -542,19 +596,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pre_training</t>
+          <t>raw_dataset_selection</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:08:04 UTC</t>
+          <t>2026-06-16 11:23:06 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,33 +454,6 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>raw_dataset_selection</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>filtercake_sugar_average_to_date</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>average_to_date</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>removed_from_X</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Column name contains an automatic target-leakage marker.</t>
         </is>
       </c>
     </row>
@@ -528,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>raw_dataset_selection</t>
+          <t>pre_training</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -596,16 +569,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>raw_dataset_selection</t>
+          <t>pre_training</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:23:06 UTC</t>
+          <t>2026-06-16 11:44:39 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:44:39 UTC</t>
+          <t>2026-06-16 14:02:36 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:02:36 UTC</t>
+          <t>2026-06-16 15:10:38 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:10:38 UTC</t>
+          <t>2026-06-16 15:30:24 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:30:24 UTC</t>
+          <t>2026-06-16 15:41:40 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:41:40 UTC</t>
+          <t>2026-06-16 16:27:50 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,33 +495,6 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>pre_training</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>white_total_points</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>kept_as_final_target</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Selected final targets are not removed from y.</t>
         </is>
       </c>
     </row>
@@ -574,14 +547,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 16:27:50 UTC</t>
+          <t>2026-06-16 17:02:33 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pre_training</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kept_as_final_target</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Selected final targets are not removed from y.</t>
         </is>
       </c>
     </row>
@@ -547,14 +574,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:02:33 UTC</t>
+          <t>2026-06-16 17:20:44 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:20:44 UTC</t>
+          <t>2026-06-16 18:08:32 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:08:32 UTC</t>
+          <t>2026-06-16 19:00:48 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:52:55 UTC</t>
+          <t>2026-06-16 19:22:10 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\tadbirsabz\Desktop\zeinab\NN\reports\leakage_report.xlsx</t>
+          <t>E:\zeinab 25 khordad\zeinab\NN\reports\leakage_report.xlsx</t>
         </is>
       </c>
     </row>

--- a/NN/reports/leakage_report.xlsx
+++ b/NN/reports/leakage_report.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pre_training</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kept_as_final_target</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Selected final targets are not removed from y.</t>
         </is>
       </c>
     </row>
@@ -547,18 +574,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:22:10 UTC</t>
+          <t>2026-06-16 20:24:52 UTC</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>E:\zeinab 25 khordad\zeinab\NN\reports\leakage_report.xlsx</t>
+          <t>C:\Users\tadbirsabz\Desktop\zeinab\NN\reports\leakage_report.xlsx</t>
         </is>
       </c>
     </row>
